--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N56_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.05909361975597</v>
+        <v>5.859602713210346</v>
       </c>
       <c r="D2" t="n">
-        <v>96.07943683094855</v>
+        <v>15.61290848502914</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
